--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$257</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AB1006</t>
+          <t>AB1011</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Med inriktning mot industriell verksamhet och tekniska system, ska studenten efter genomgången kurs, kunna:…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1011</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AB1009</t>
+          <t>AB1014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': På en övergripande nivå är kursens mål att studenten efter avklarad kurs ska:…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1014</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AB1014</t>
+          <t>AB1015</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,1642 +536,6853 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kompetens att genomföra verksamhetsutveckling genom ordn…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1015</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FI1029</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig översiktliga kunskaper kring de regler och den omvärld s…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>AB1022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att inför en rekrytering kunna göra en relevant kravspecifikation för en anställning. Efter …</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HI1011</t>
+          <t>AB1024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren ska kunna formulera en plan för genomförandet av en kreativ idéutveckling…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1024</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KG1005</t>
+          <t>AB1025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KG1010</t>
+          <t>AB1026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>AB1027</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KG1020</t>
+          <t>AB1028</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet, ska utveckla en fördjupad f…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1028</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KG1021</t>
+          <t>AB1029</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig förmåga att relatera relevant forskning och teo…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>AB1030</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kompetens för att arbeta effektivt i projekt.…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1030</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>AB1031</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kompetens för att på arbetsplatser arbeta effektivt med …</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1031</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>AB1032</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1032</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KG1027</t>
+          <t>AB1033</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla ett normkritiskt förhållningssätt vad gäller genus och m…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1033</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>GAB24E</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande, med utgångspunkt i sin specifika ledarroll och relevanta teorie…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24E</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KG2003</t>
+          <t>GAB24F</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper om hur man på arbetsplatser kan …</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>GAB26D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB26D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>GAB2AJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2AJ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>GAB2CC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2CC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>GAB2P6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig förmåga att på ett professionellt sätt kommunicera…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2P6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>NA1025</t>
+          <t>GAB2S5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att ge grundläggande kunskaper och färdigheter för att kunna förebygga och minimera…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>GAB2TR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att deltagarna utifrån ett stödjande förhållningssätt ska kunna bistå processledare…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>GAB358</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål kopplas till studentens egna ledarskap.…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>ABP253</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NA2001</t>
+          <t>ABP254</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>GBP32U</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för bildundervisning i grundskolans tidigare år. Målet är att den studerande efter avslutad kurs har k…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32U</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NA3007</t>
+          <t>GBP32V</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för bildundervisning i grundskolans tidigare år. Målet är att den studerande efter avslutad kurs har k…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32V</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>GBP32W</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för bildundervisning i grundskolan och gymnasieskolan. Det övergripande målet är att den studerande ef…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32W</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PE1032</t>
+          <t>GBP34H</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för undervisning i ämnet bild i grundskolans senare år och i gymnasieskolan. Det övergripande syftet ä…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP34H</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PE1074</t>
+          <t>GBP365</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för undervisning i ämnet bild i gymnasieskolan. Målet är att den studerande efter avslutad kurs har up…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP365</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PE1075</t>
+          <t>BQ1081</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1081</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PE1076</t>
+          <t>BQ1094</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter fullbordad kurs kunna:…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1094</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>PE3002</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PE3003</t>
+          <t>EU1033</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>EU1034</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>EU1035</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1035</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>EU1036</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1036</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>EU1037</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1037</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GEU2CA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GEU2CB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GEU2KW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GEU2KX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GEU2QY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>FI1026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursen mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>FI1028</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna visa:**…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>FI1029</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska:**…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1029</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>FI1030</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1030</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>FI1031</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>FI1033</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>FI1034</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>FI1035</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>FI1036</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>FI1037</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>FI1038</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>FI1040</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1040</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GFI293</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Saknar punktlista med lärandemål</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GHI2CN</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GHI2CP</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GHI2CQ</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och i fråga om någo…</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GHI2CR</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och historiedidakti…</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GHI32G</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GHI33T</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria. D…</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GHI33W</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning, de nationella minor…</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GHI362</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om historieämnets utveckling, samt dess teori- och metod…</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GHI374</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GHI378</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om den moderna och samtida globalhistorien, de nationella mino…</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GHI3JX</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning. Dessutom fördjupar …</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>HI1004</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna: **…</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>HI1006</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en översiktlig kunskap om de globala rörelser och organisationer som arbetar för att skapa en ny världsordnin…</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>HI1011</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>HI1013</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper inom fälten den globala ekonomins historia och historied…</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>HI1014</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och miljöhistoria. Den…</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1014</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>HI1015</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och historiedidaktik. …</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>HI1018</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>HI1019</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>HI2011</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>HI2012</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>HI2013</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>HI2014</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning oc…</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>HI2016</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>HI2017</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>HI3020</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om förintelseforskningen och nya perspektiv inom denna,…</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>KG1005</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha kunskaper om:…</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>KG1022</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med denna kurs är att studenten skall:…</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenter antas till kursen i sin helhet men kursen är uppbyggd av tre moduler som examineras i tur och ordning…</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>KG2003</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destination…</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>KG2005</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>KG3010</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha:…</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>KG3014</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>KG3015</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>KG3016</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig och utveckla kunskaper, färdigheter och förmågor g…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>KG3018</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3018</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ANA235</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ANA235</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>NA1003</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>NA1024</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Mikroekonomi belyser samspelet mellan konsumenter och producenter i en marknadsekonomi och vad utfallet blir av detta sa…</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>NA1025</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge studenterna kunskaper om olika makroekonomiska frågeställningar:…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>NA1026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>NA1027</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till grundläggande ekonomiska teorier om världsekonomin. Syftet är att studenten efter genomg…</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>NA1029</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenterna skaffar sig förmågor och färdigheter att tillämpa matematiska metoder för at…</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>NA1030</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska tillägna sig grundläggande kunskaper om ekonomiska teorier om världsekonomin…</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>NA1031</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig kunskap om teori och tillämpning av ekonometriska metoder. Efter g…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>NA1032</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig kunskaper om olika makroekonomiska frågeställninga…</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>NA1033</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig fördjupade insikter i olika ekonomiska teorier och analysmetoder…</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>NA1035</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig grundläggande kunskap om de begrepp och metoder som …</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>NA2001</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs:…</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>NA3001</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en avancerad behandling av hur mikroekonomi kan användas för att analysera samhällsproblem med särskild tonvi…</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>NA3005</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>NA3007</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Samhällsekonomiska kalkyler (eller Cost Benefit Analysis, CBA, som de också kallas) är en metod som används inom olika s…</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>NA3008</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen behandlar matematiska metoder för statisk optimering. Efter genomgången kurs skall studenten kunna förstår och ha…</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>NA3010</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>NA3011</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig färdigheter att konstruera avancerade ekonometriska modeller med h…</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GPE3AJ</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>PE1011</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande skall vidareutveckla sin kunskap om och förståelse för lärande …</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>PE1018</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>PE1020</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>PE1021</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i att dokumentera och upprätta utvecklingsp…</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>PE1023</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är…</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>PE1039</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>PE1050</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>PE1052</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>PE1055</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>PE1057</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>PE1058</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>PE1062</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>PE1063</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>PE1064</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>PE1065</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>PE1066</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>PE1067</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt …</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>PE1068</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>PE1069</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>PE1070</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>PE1071</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>PE1072</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>PE1073</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>PE1074</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>PE1075</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>PE1076</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>PE1077</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>PE2005</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>PE2017</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>PE3003</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>PE3012</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>GPA2FL</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>GPA2FW</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>GPA2K3</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GPA2KU</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GPA2LM</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GPA2LN</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GPA2NY</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GPA2P7</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GPA2R6</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GPA32D</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GPA32E</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>PA2008</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>PA2009</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>PA2010</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>PA2011</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>APG22X</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>APG244</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>APG245</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>APG24D</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>APG24S</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>APG25N</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>APG26D</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>APG275</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>APG27Z</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>APG29G</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>APG2BC</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>GPG22J</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>GPG22K</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>GPG27X</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>GPG2LZ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>GPG2M9</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>GPG2QP</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RH</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RR</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RS</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>GPG2S7</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>GPG2S8</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>GPG2S9</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>GPG2VW</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>GPG2YG</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>GPG36A</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>GPG36B</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CF</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CG</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CH</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CJ</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>GPG3EU</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>GPG3EV</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FR</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>GPG3JD</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>PG2043</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>PG2048</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>PG3023</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>PG3024</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>PG3025</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>PG3031</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>PG3041</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>PG3056</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>PG3061</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>PG3069</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>GRK2P3</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>GRK2P4</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>GRK2Q5</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>GRK324</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>RK1068</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>GRV22R</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>GRV2FC</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>GRV2MK</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>GRV3BF</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>RV1037</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>RV1045</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>RV1046</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>RV1047</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>RV1048</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>RV1049</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>RV1050</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>RV1051</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>RV1052</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>RV1053</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>RV1054</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>RV1056</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>RV1057</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>RV1058</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>GSO2PL</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>GSO2UA</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XU</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XV</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>GSO33U</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>SO1030</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>SO1044</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DP</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Saknar introfras</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Saknar punktlista med lärandemål</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>TR2005</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>TR3008</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>TR3010</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>AS4001</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>AS4002</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E64"/>
+  <autoFilter ref="A1:E257"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2299,6 +7510,392 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1363,7 +1363,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EU1027</t>
+          <t>GEU2QY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': _Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EU1033</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EU1034</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EU1035</t>
+          <t>FI1026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursen mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EU1036</t>
+          <t>FI1028</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna visa:**…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EU1037</t>
+          <t>FI1029</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska:**…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1029</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GEU2CA</t>
+          <t>FI1030</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1030</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GEU2CB</t>
+          <t>FI1031</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1033</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GEU2KW</t>
+          <t>FI1034</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GEU2KX</t>
+          <t>FI1035</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GEU2QY</t>
+          <t>FI1036</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>FI1037</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>FI1038</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FI1026</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursen mål är att den studerande efter genomgången kurs ska kunna:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FI1028</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna visa:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FI1029</t>
+          <t>GFI293</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FI1030</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FI1031</t>
+          <t>GHI2CN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FI1033</t>
+          <t>GHI2CP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FI1034</t>
+          <t>GHI2CQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och i fråga om någo…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FI1035</t>
+          <t>GHI2CR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och historiedidakti…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FI1036</t>
+          <t>GHI32G</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FI1037</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria. D…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FI1038</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>GHI33W</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FI1040</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning, de nationella minor…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om historieämnets utveckling, samt dess teori- och metod…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GFI293</t>
+          <t>GHI374</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GHI378</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om den moderna och samtida globalhistorien, de nationella mino…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GHI2CN</t>
+          <t>GHI3JX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning. Dessutom fördjupar …</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GHI2CP</t>
+          <t>HI1004</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna: **…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GHI2CQ</t>
+          <t>HI1006</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och i fråga om någo…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en översiktlig kunskap om de globala rörelser och organisationer som arbetar för att skapa en ny världsordnin…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GHI2CR</t>
+          <t>HI1011</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och historiedidakti…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GHI32G</t>
+          <t>HI1013</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper inom fälten den globala ekonomins historia och historied…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>HI1014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria. D…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och miljöhistoria. Den…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1014</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>HI1015</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och historiedidaktik. …</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GHI33W</t>
+          <t>HI1018</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1018</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI1019</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning, de nationella minor…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1019</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om historieämnets utveckling, samt dess teori- och metod…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GHI374</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GHI378</t>
+          <t>HI2013</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om den moderna och samtida globalhistorien, de nationella mino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2013</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GHI3JX</t>
+          <t>HI2014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning. Dessutom fördjupar …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning oc…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HI1004</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna: **…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HI1006</t>
+          <t>HI2017</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en översiktlig kunskap om de globala rörelser och organisationer som arbetar för att skapa en ny världsordnin…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HI1011</t>
+          <t>HI3020</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om förintelseforskningen och nya perspektiv inom denna,…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3020</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>HI1013</t>
+          <t>KG1005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper inom fälten den globala ekonomins historia och historied…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha kunskaper om:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>HI1014</t>
+          <t>KG1022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och miljöhistoria. Den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med denna kurs är att studenten skall:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>HI1015</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och historiedidaktik. …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenter antas till kursen i sin helhet men kursen är uppbyggd av tre moduler som examineras i tur och ordning…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>HI1018</t>
+          <t>KG2003</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destination…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2003</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>HI1019</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>HI2013</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>HI2014</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig och utveckla kunskaper, färdigheter och förmågor g…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>KG3018</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3018</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>HI2017</t>
+          <t>ANA235</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ANA235</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>HI3020</t>
+          <t>NA1003</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om förintelseforskningen och nya perspektiv inom denna,…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KG1005</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha kunskaper om:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Mikroekonomi belyser samspelet mellan konsumenter och producenter i en marknadsekonomi och vad utfallet blir av detta sa…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>NA1025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med denna kurs är att studenten skall:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge studenterna kunskaper om olika makroekonomiska frågeställningar:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenter antas till kursen i sin helhet men kursen är uppbyggd av tre moduler som examineras i tur och ordning…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KG2003</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destination…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till grundläggande ekonomiska teorier om världsekonomin. Syftet är att studenten efter genomg…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenterna skaffar sig förmågor och färdigheter att tillämpa matematiska metoder för at…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska tillägna sig grundläggande kunskaper om ekonomiska teorier om världsekonomin…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>NA1031</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig kunskap om teori och tillämpning av ekonometriska metoder. Efter g…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1031</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig kunskaper om olika makroekonomiska frågeställninga…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>NA1033</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig och utveckla kunskaper, färdigheter och förmågor g…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig fördjupade insikter i olika ekonomiska teorier och analysmetoder…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1033</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>KG3018</t>
+          <t>NA1035</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig grundläggande kunskap om de begrepp och metoder som …</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ANA235</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3219,14 +3219,14 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ANA235</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>NA2001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Mikroekonomi belyser samspelet mellan konsumenter och producenter i en marknadsekonomi och vad utfallet blir av detta sa…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>NA1025</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge studenterna kunskaper om olika makroekonomiska frågeställningar:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en avancerad behandling av hur mikroekonomi kan användas för att analysera samhällsproblem med särskild tonvi…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA3005</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA3007</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till grundläggande ekonomiska teorier om världsekonomin. Syftet är att studenten efter genomg…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Samhällsekonomiska kalkyler (eller Cost Benefit Analysis, CBA, som de också kallas) är en metod som används inom olika s…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>NA3008</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenterna skaffar sig förmågor och färdigheter att tillämpa matematiska metoder för at…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen behandlar matematiska metoder för statisk optimering. Efter genomgången kurs skall studenten kunna förstår och ha…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska tillägna sig grundläggande kunskaper om ekonomiska teorier om världsekonomin…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NA1031</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig kunskap om teori och tillämpning av ekonometriska metoder. Efter g…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig färdigheter att konstruera avancerade ekonometriska modeller med h…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig kunskaper om olika makroekonomiska frågeställninga…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>NA1033</t>
+          <t>PE1011</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig fördjupade insikter i olika ekonomiska teorier och analysmetoder…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande skall vidareutveckla sin kunskap om och förståelse för lärande …</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>PE1018</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig grundläggande kunskap om de begrepp och metoder som …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NA2001</t>
+          <t>PE1021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i att dokumentera och upprätta utvecklingsp…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>PE1039</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en avancerad behandling av hur mikroekonomi kan användas för att analysera samhällsproblem med särskild tonvi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>NA3005</t>
+          <t>PE1050</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>NA3007</t>
+          <t>PE1052</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Samhällsekonomiska kalkyler (eller Cost Benefit Analysis, CBA, som de också kallas) är en metod som används inom olika s…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>NA3008</t>
+          <t>PE1055</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen behandlar matematiska metoder för statisk optimering. Efter genomgången kurs skall studenten kunna förstår och ha…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>PE1057</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>PE1058</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig färdigheter att konstruera avancerade ekonometriska modeller med h…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>PE1062</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>PE1011</t>
+          <t>PE1063</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande skall vidareutveckla sin kunskap om och förståelse för lärande …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PE1018</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>PE1065</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>PE1066</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i att dokumentera och upprätta utvecklingsp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt …</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>PE1039</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>PE1050</t>
+          <t>PE1069</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3970,19 +3970,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>PE1052</t>
+          <t>PE1070</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>PE1055</t>
+          <t>PE1071</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4024,19 +4024,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>PE1057</t>
+          <t>PE1072</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PE1058</t>
+          <t>PE1073</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>PE1062</t>
+          <t>PE1074</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4105,19 +4105,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>PE1063</t>
+          <t>PE1075</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>PE1076</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PE1065</t>
+          <t>PE1077</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>PE1066</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4213,19 +4213,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>PE2017</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>PE3003</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4267,19 +4267,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PE1069</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>PE1070</t>
+          <t>PE3012</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>PE1071</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>PE1072</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>PE1073</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>PE1074</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>PE1075</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,24 +4456,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>PE1076</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4483,24 +4483,24 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PE1077</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PE2017</t>
+          <t>GPA32E</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PE3003</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PE3012</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>APG22X</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>APG24D</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GPA32E</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>APG29G</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>APG22X</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>APG24D</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,19 +5509,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5563,19 +5563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5590,19 +5590,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5622,14 +5622,14 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5649,14 +5649,14 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG3JD</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,19 +5725,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5752,19 +5752,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5779,19 +5779,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5860,19 +5860,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5887,19 +5887,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5941,19 +5941,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5968,19 +5968,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>PG3069</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GPG3JD</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>RV1046</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande skall efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>PG3069</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6508,19 +6508,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6535,19 +6535,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6562,19 +6562,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6589,19 +6589,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,24 +6724,24 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6751,24 +6751,24 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6778,24 +6778,24 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6805,24 +6805,24 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>TR2005</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6832,24 +6832,24 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>TR3008</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6859,24 +6859,24 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>AS4001</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6886,24 +6886,24 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>AS4002</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6913,476 +6913,17 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>RV1056</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>RV1057</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>RV1058</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>GSO2PL</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>GSO2UA</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>GSO2XU</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>GSO2XV</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>GSO33U</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>SO1030</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>SO1044</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>GTR2DP</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>TR2005</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>TR3008</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>TR3010</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>AS4001</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>AS4002</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E257"/>
+  <autoFilter ref="A1:E240"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -7862,40 +7403,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$235</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E240"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1363,12 +1363,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GEU2QY</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>FI1026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursen mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FI1026</t>
+          <t>FI1028</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursen mål är att den studerande efter genomgången kurs ska kunna:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna visa:**…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FI1028</t>
+          <t>FI1029</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna visa:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska:**…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1029</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FI1029</t>
+          <t>FI1030</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1030</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FI1030</t>
+          <t>FI1031</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FI1031</t>
+          <t>FI1033</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FI1033</t>
+          <t>FI1034</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FI1034</t>
+          <t>FI1035</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FI1035</t>
+          <t>FI1036</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FI1036</t>
+          <t>FI1037</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FI1037</t>
+          <t>FI1038</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FI1038</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>GFI293</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GFI293</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GHI2CN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GHI2CN</t>
+          <t>GHI2CP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1869,14 +1869,14 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GHI2CP</t>
+          <t>GHI2CQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och i fråga om någo…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GHI2CQ</t>
+          <t>GHI2CR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och i fråga om någo…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och historiedidakti…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GHI2CR</t>
+          <t>GHI32G</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och historiedidakti…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GHI32G</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria. D…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria. D…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>GHI33W</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2031,14 +2031,14 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GHI33W</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning, de nationella minor…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning, de nationella minor…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om historieämnets utveckling, samt dess teori- och metod…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>GHI374</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om historieämnets utveckling, samt dess teori- och metod…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GHI374</t>
+          <t>GHI378</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om den moderna och samtida globalhistorien, de nationella mino…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GHI378</t>
+          <t>GHI3JX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om den moderna och samtida globalhistorien, de nationella mino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning. Dessutom fördjupar …</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GHI3JX</t>
+          <t>HI1004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning. Dessutom fördjupar …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna: **…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>HI1004</t>
+          <t>HI1006</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna: **…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en översiktlig kunskap om de globala rörelser och organisationer som arbetar för att skapa en ny världsordnin…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>HI1006</t>
+          <t>HI1011</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en översiktlig kunskap om de globala rörelser och organisationer som arbetar för att skapa en ny världsordnin…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>HI1011</t>
+          <t>HI1013</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper inom fälten den globala ekonomins historia och historied…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1013</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HI1013</t>
+          <t>HI1014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper inom fälten den globala ekonomins historia och historied…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och miljöhistoria. Den…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1014</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HI1014</t>
+          <t>HI1015</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och miljöhistoria. Den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och historiedidaktik. …</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>HI1015</t>
+          <t>HI1018</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och historiedidaktik. …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1018</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HI1018</t>
+          <t>HI1019</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1019</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>HI1019</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>HI2013</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2013</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>HI2013</t>
+          <t>HI2014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning oc…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>HI2014</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>HI2017</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HI2017</t>
+          <t>HI3020</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om förintelseforskningen och nya perspektiv inom denna,…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3020</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HI3020</t>
+          <t>KG1005</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om förintelseforskningen och nya perspektiv inom denna,…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha kunskaper om:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>KG1005</t>
+          <t>KG1022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha kunskaper om:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med denna kurs är att studenten skall:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med denna kurs är att studenten skall:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenter antas till kursen i sin helhet men kursen är uppbyggd av tre moduler som examineras i tur och ordning…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG2003</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenter antas till kursen i sin helhet men kursen är uppbyggd av tre moduler som examineras i tur och ordning…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destination…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2003</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KG2003</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destination…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2787,14 +2787,14 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig och utveckla kunskaper, färdigheter och förmågor g…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>KG3018</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig och utveckla kunskaper, färdigheter och förmågor g…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3018</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>KG3018</t>
+          <t>ANA235</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ANA235</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ANA235</t>
+          <t>NA1003</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ANA235</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Mikroekonomi belyser samspelet mellan konsumenter och producenter i en marknadsekonomi och vad utfallet blir av detta sa…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA1025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Mikroekonomi belyser samspelet mellan konsumenter och producenter i en marknadsekonomi och vad utfallet blir av detta sa…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge studenterna kunskaper om olika makroekonomiska frågeställningar:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>NA1025</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge studenterna kunskaper om olika makroekonomiska frågeställningar:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till grundläggande ekonomiska teorier om världsekonomin. Syftet är att studenten efter genomg…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till grundläggande ekonomiska teorier om världsekonomin. Syftet är att studenten efter genomg…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenterna skaffar sig förmågor och färdigheter att tillämpa matematiska metoder för at…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenterna skaffar sig förmågor och färdigheter att tillämpa matematiska metoder för at…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska tillägna sig grundläggande kunskaper om ekonomiska teorier om världsekonomin…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>NA1031</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska tillägna sig grundläggande kunskaper om ekonomiska teorier om världsekonomin…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig kunskap om teori och tillämpning av ekonometriska metoder. Efter g…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1031</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NA1031</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig kunskap om teori och tillämpning av ekonometriska metoder. Efter g…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig kunskaper om olika makroekonomiska frågeställninga…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>NA1033</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig kunskaper om olika makroekonomiska frågeställninga…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig fördjupade insikter i olika ekonomiska teorier och analysmetoder…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1033</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NA1033</t>
+          <t>NA1035</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig fördjupade insikter i olika ekonomiska teorier och analysmetoder…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig grundläggande kunskap om de begrepp och metoder som …</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig grundläggande kunskap om de begrepp och metoder som …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>NA2001</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs:…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>NA2001</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en avancerad behandling av hur mikroekonomi kan användas för att analysera samhällsproblem med särskild tonvi…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>NA3005</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en avancerad behandling av hur mikroekonomi kan användas för att analysera samhällsproblem med särskild tonvi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>NA3005</t>
+          <t>NA3007</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Samhällsekonomiska kalkyler (eller Cost Benefit Analysis, CBA, som de också kallas) är en metod som används inom olika s…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>NA3007</t>
+          <t>NA3008</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Samhällsekonomiska kalkyler (eller Cost Benefit Analysis, CBA, som de också kallas) är en metod som används inom olika s…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen behandlar matematiska metoder för statisk optimering. Efter genomgången kurs skall studenten kunna förstår och ha…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>NA3008</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen behandlar matematiska metoder för statisk optimering. Efter genomgången kurs skall studenten kunna förstår och ha…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig färdigheter att konstruera avancerade ekonometriska modeller med h…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig färdigheter att konstruera avancerade ekonometriska modeller med h…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>PE1011</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande skall vidareutveckla sin kunskap om och förståelse för lärande …</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PE1011</t>
+          <t>PE1018</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande skall vidareutveckla sin kunskap om och förståelse för lärande …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PE1018</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3516,14 +3516,14 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>PE1021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i att dokumentera och upprätta utvecklingsp…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i att dokumentera och upprätta utvecklingsp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE1039</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PE1039</t>
+          <t>PE1050</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PE1050</t>
+          <t>PE1052</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PE1052</t>
+          <t>PE1055</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3673,19 +3673,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PE1055</t>
+          <t>PE1057</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PE1057</t>
+          <t>PE1058</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>PE1058</t>
+          <t>PE1062</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>PE1062</t>
+          <t>PE1063</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>PE1063</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>PE1065</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>PE1065</t>
+          <t>PE1066</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>PE1066</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt …</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>PE1069</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>PE1069</t>
+          <t>PE1070</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3970,19 +3970,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>PE1070</t>
+          <t>PE1071</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>PE1071</t>
+          <t>PE1072</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4024,19 +4024,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>PE1072</t>
+          <t>PE1073</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PE1073</t>
+          <t>PE1074</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>PE1074</t>
+          <t>PE1075</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4110,14 +4110,14 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>PE1075</t>
+          <t>PE1076</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>PE1076</t>
+          <t>PE1077</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PE1077</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>PE2017</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4213,19 +4213,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PE2017</t>
+          <t>PE3003</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>PE3003</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4267,19 +4267,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>PE3012</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>PE3012</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,19 +4321,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4375,19 +4375,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4402,19 +4402,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4429,19 +4429,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4456,19 +4456,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4483,19 +4483,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>GPA32E</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GPA32E</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,19 +4564,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,19 +4618,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>APG22X</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>APG22X</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4699,19 +4699,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>APG24D</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4753,19 +4753,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>APG24D</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4780,19 +4780,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4861,19 +4861,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4915,19 +4915,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,19 +4942,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>APG29G</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,19 +4996,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5023,19 +5023,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5190,14 +5190,14 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5217,14 +5217,14 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5271,14 +5271,14 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5379,14 +5379,14 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5460,14 +5460,14 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5514,14 +5514,14 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5590,19 +5590,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5622,14 +5622,14 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5649,14 +5649,14 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3JD</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GPG3JD</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,19 +5725,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5779,19 +5779,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5838,14 +5838,14 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5860,19 +5860,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5887,19 +5887,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5941,19 +5941,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>PG3069</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>PG3069</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5995,19 +5995,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6022,19 +6022,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6049,19 +6049,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6076,19 +6076,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,19 +6130,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6157,19 +6157,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6184,19 +6184,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6238,19 +6238,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande skall efter avslutad kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,19 +6373,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6400,19 +6400,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6427,19 +6427,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6459,14 +6459,14 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6481,19 +6481,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6508,19 +6508,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>TR2005</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>TR3008</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,24 +6724,24 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>AS4001</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6751,24 +6751,24 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>AS4002</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6778,152 +6778,17 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Studenten skall efter avslutad kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>TR2005</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>TR3008</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>AS4001</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>AS4002</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E240"/>
+  <autoFilter ref="A1:E235"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -7393,16 +7258,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna: **…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna:**…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E235"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4306,12 +4306,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>FPA0001</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att ge forskarstuderande en introduktion till olika forskningsmetoder samt stödja …</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att de forskarstuderande utvecklar fördjupad kunskap om forskning om läsinlärning o…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de forskarstuderande utvecklarfördjupade kunskaper om vetenskapsteori och forskningsetik…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen avser att ge en introduktion till och en översikt av grundläggande statistiska begrepp och deras tillämpning i kv…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,19 +4456,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4483,19 +4483,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GPA32E</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,19 +4564,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,19 +4618,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>APG22X</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>GPA32E</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>APG24D</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>APG22X</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4861,19 +4861,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>APG24D</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4915,19 +4915,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,19 +4942,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,19 +4996,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5023,19 +5023,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>APG29G</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5379,14 +5379,14 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5460,14 +5460,14 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,19 +5509,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5563,19 +5563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5595,14 +5595,14 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5622,14 +5622,14 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5644,19 +5644,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPG3JD</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,19 +5725,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5752,19 +5752,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5779,19 +5779,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>GPG3JD</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5860,19 +5860,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5887,19 +5887,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5941,19 +5941,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>PG3069</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>PG3069</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,19 +6373,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6400,19 +6400,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6427,19 +6427,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6454,19 +6454,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6481,19 +6481,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6508,19 +6508,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>TR2005</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>TR3008</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,24 +6724,24 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>AS4001</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6751,44 +6751,206 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
+          <t>GSO2XV</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>GSO33U</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>TR2005</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>TR3008</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>AS4001</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
           <t>AS4002</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E235"/>
+  <autoFilter ref="A1:E241"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -7258,6 +7420,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2010-04-20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Med inriktning mot industriell verksamhet och tekniska system, ska studenten efter genomgången kurs, kunna:…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1011</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2011-04-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': På en övergripande nivå är kursens mål att studenten efter avklarad kurs ska:…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1014</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2011-09-14</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kompetens att genomföra verksamhetsutveckling genom ordn…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1015</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig översiktliga kunskaper kring de regler och den omvärld s…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2013-06-13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att inför en rekrytering kunna göra en relevant kravspecifikation för en anställning. Efter …</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2014-02-20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren ska kunna formulera en plan för genomförandet av en kreativ idéutveckling…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1024</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2014-12-11</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1025</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2014-12-11</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1026</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2014-12-11</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1027</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2015-01-15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet, ska utveckla en fördjupad f…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1028</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig förmåga att relatera relevant forskning och teo…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
@@ -779,15 +857,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2016-03-09</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kompetens för att arbeta effektivt i projekt.…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1030</t>
         </is>
@@ -806,15 +890,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kompetens för att på arbetsplatser arbeta effektivt med …</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1031</t>
         </is>
@@ -833,15 +923,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1032</t>
         </is>
@@ -860,15 +956,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska utveckla ett normkritiskt förhållningssätt vad gäller genus och m…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1033</t>
         </is>
@@ -887,15 +989,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande, med utgångspunkt i sin specifika ledarroll och relevanta teorie…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24E</t>
         </is>
@@ -914,15 +1022,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper om hur man på arbetsplatser kan …</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24F</t>
         </is>
@@ -941,15 +1055,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB26D</t>
         </is>
@@ -968,15 +1088,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2AJ</t>
         </is>
@@ -995,15 +1121,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2019-12-02</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, med utgångspunkt i det egna ledarskapet och relevanta teorier, ska u…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2CC</t>
         </is>
@@ -1022,15 +1154,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten skall tillägna sig förmåga att på ett professionellt sätt kommunicera…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2P6</t>
         </is>
@@ -1049,15 +1187,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att ge grundläggande kunskaper och färdigheter för att kunna förebygga och minimera…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
         </is>
@@ -1076,15 +1220,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2021-12-07</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att deltagarna utifrån ett stödjande förhållningssätt ska kunna bistå processledare…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
         </is>
@@ -1103,15 +1253,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål kopplas till studentens egna ledarskap.…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
         </is>
@@ -1130,15 +1286,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
         </is>
@@ -1157,15 +1319,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
         </is>
@@ -1184,15 +1352,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för bildundervisning i grundskolans tidigare år. Målet är att den studerande efter avslutad kurs har k…</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32U</t>
         </is>
@@ -1211,15 +1385,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för bildundervisning i grundskolans tidigare år. Målet är att den studerande efter avslutad kurs har k…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32V</t>
         </is>
@@ -1238,15 +1418,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för bildundervisning i grundskolan och gymnasieskolan. Det övergripande målet är att den studerande ef…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32W</t>
         </is>
@@ -1265,15 +1451,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för undervisning i ämnet bild i grundskolans senare år och i gymnasieskolan. Det övergripande syftet ä…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP34H</t>
         </is>
@@ -1292,15 +1484,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen förbereder för undervisning i ämnet bild i gymnasieskolan. Målet är att den studerande efter avslutad kurs har up…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP365</t>
         </is>
@@ -1319,15 +1517,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2014-08-25</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1081</t>
         </is>
@@ -1346,15 +1550,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2015-12-10</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter fullbordad kurs kunna:…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1094</t>
         </is>
@@ -1373,15 +1583,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
@@ -1400,15 +1620,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>2020-07-06</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
@@ -1427,15 +1657,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Kursen mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
         </is>
@@ -1454,15 +1694,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna visa:**…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
         </is>
@@ -1481,15 +1731,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska:**…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1029</t>
         </is>
@@ -1508,15 +1768,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1030</t>
         </is>
@@ -1535,15 +1805,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
         </is>
@@ -1562,15 +1842,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>2015-10-23</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
         </is>
@@ -1589,15 +1879,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>2019-03-18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
         </is>
@@ -1616,15 +1916,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
         </is>
@@ -1643,15 +1953,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
         </is>
@@ -1670,15 +1990,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen mål är att den studerande efter genomgången kurs ska kunna:…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
         </is>
@@ -1697,15 +2027,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-10-19</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
         </is>
@@ -1724,15 +2064,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2011-05-30</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
@@ -1751,15 +2101,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>2020-07-06</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Kursens mål är att den studerande efter genomgången kurs ska kunna:**…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
@@ -1778,15 +2138,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2019-04-04</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter genomgången kurs ska kunna visa:…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
         </is>
@@ -1805,15 +2171,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
@@ -1832,15 +2204,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
         </is>
@@ -1859,15 +2237,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
         </is>
@@ -1886,15 +2270,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och i fråga om någo…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
         </is>
@@ -1913,15 +2303,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om modern och samtida globalhistoria och historiedidakti…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
         </is>
@@ -1940,15 +2336,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
         </is>
@@ -1967,15 +2369,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria. D…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
@@ -1994,15 +2406,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
@@ -2021,15 +2439,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar insikter och kunskaper om för historieämnet grundläggande vetenskapliga…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
         </is>
@@ -2048,15 +2476,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning, de nationella minor…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
@@ -2075,15 +2509,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om historieämnets utveckling, samt dess teori- och metod…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
@@ -2102,15 +2546,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att studenten fördjupar sina kunskaper om äldre och nyare historia samt om samtida globalhistoria oc…</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
         </is>
@@ -2129,15 +2579,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om den moderna och samtida globalhistorien, de nationella mino…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
         </is>
@@ -2156,15 +2612,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande inhämtar kunskaper om kulturstudier med historisk inriktning. Dessutom fördjupar …</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
         </is>
@@ -2183,15 +2645,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-01-09</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Efter genomgången kurs ska studenten kunna:**…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
         </is>
@@ -2210,15 +2682,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2009-05-28</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en översiktlig kunskap om de globala rörelser och organisationer som arbetar för att skapa en ny världsordnin…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
         </is>
@@ -2237,15 +2719,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2012-08-20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
         </is>
@@ -2264,15 +2752,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper inom fälten den globala ekonomins historia och historied…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1013</t>
         </is>
@@ -2291,15 +2785,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2013-03-11</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och miljöhistoria. Den…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1014</t>
         </is>
@@ -2318,15 +2818,25 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-03-11</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>2019-03-27</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande fördjupar sina kunskaper om den globala ekonomins historia och historiedidaktik. …</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
         </is>
@@ -2345,15 +2855,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2016-12-20</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1018</t>
         </is>
@@ -2372,15 +2888,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2016-12-20</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska under kursen utveckla kunskaper om grundläggande vetenskapliga, didaktiska och metodologiska frågor o…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1019</t>
         </is>
@@ -2399,15 +2921,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning, u…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
@@ -2426,15 +2954,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
@@ -2453,15 +2987,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2013</t>
         </is>
@@ -2480,15 +3020,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar kunskaper om kulturstudier med historisk inriktning oc…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2014</t>
         </is>
@@ -2507,15 +3053,25 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sin kunskaper om teori- och metodanvändning inom hi…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
@@ -2534,15 +3090,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska fördjupa sina kunskaper om teori- och metodanvändning inom h…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
         </is>
@@ -2561,15 +3127,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om förintelseforskningen och nya perspektiv inom denna,…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3020</t>
         </is>
@@ -2588,15 +3160,25 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-03-16</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>2010-09-14</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha kunskaper om:…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
         </is>
@@ -2615,15 +3197,25 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-02-23</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>2012-11-28</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Syftet med denna kurs är att studenten skall:…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
@@ -2642,15 +3234,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-05-30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>2011-12-22</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenter antas till kursen i sin helhet men kursen är uppbyggd av tre moduler som examineras i tur och ordning…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
@@ -2669,15 +3271,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2010-04-20</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destination…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2003</t>
         </is>
@@ -2696,15 +3304,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2014-01-30</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
@@ -2723,15 +3337,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2009-03-30</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs ha:…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
@@ -2750,15 +3370,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-04-20</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>2012-04-12</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
@@ -2777,15 +3407,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2013-02-25</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i kulturgeografi med särskild bäring på destinationsu…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
@@ -2804,15 +3440,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2013-12-12</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig och utveckla kunskaper, färdigheter och förmågor g…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
@@ -2831,15 +3473,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2014-12-11</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten förväntas efter genomgången kurs kunna:…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3018</t>
         </is>
@@ -2858,15 +3506,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2019-04-18</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ANA235</t>
         </is>
@@ -2885,15 +3539,25 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2006-12-06</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>2009-03-05</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
         </is>
@@ -2912,15 +3576,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Mikroekonomi belyser samspelet mellan konsumenter och producenter i en marknadsekonomi och vad utfallet blir av detta sa…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
@@ -2939,15 +3609,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge studenterna kunskaper om olika makroekonomiska frågeställningar:…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
         </is>
@@ -2966,15 +3642,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Vid avslutad kurs har studenten förmågan att:…</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
@@ -2993,15 +3675,25 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2009-10-19</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>2013-03-07</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till grundläggande ekonomiska teorier om världsekonomin. Syftet är att studenten efter genomg…</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
@@ -3020,15 +3712,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenterna skaffar sig förmågor och färdigheter att tillämpa matematiska metoder för at…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
@@ -3047,15 +3745,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten ska tillägna sig grundläggande kunskaper om ekonomiska teorier om världsekonomin…</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
@@ -3074,15 +3778,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig kunskap om teori och tillämpning av ekonometriska metoder. Efter g…</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1031</t>
         </is>
@@ -3101,15 +3811,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-02-21</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>2015-06-17</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenterna ska tillägna sig kunskaper om olika makroekonomiska frågeställninga…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
@@ -3128,15 +3848,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig fördjupade insikter i olika ekonomiska teorier och analysmetoder…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1033</t>
         </is>
@@ -3155,15 +3881,25 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>2015-04-22</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska tillägna sig grundläggande kunskap om de begrepp och metoder som …</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
@@ -3182,15 +3918,25 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>2020-01-19</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
@@ -3209,15 +3955,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+          <t>2007-09-06</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs:…</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
         </is>
@@ -3236,15 +3988,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
@@ -3263,15 +4021,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>2006-12-06</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en avancerad behandling av hur mikroekonomi kan användas för att analysera samhällsproblem med särskild tonvi…</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
@@ -3290,15 +4054,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+          <t>2007-09-05</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenterna skall efter genomgången kurs kunna:…</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
         </is>
@@ -3317,15 +4087,25 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-09-05</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t>2008-02-07</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Samhällsekonomiska kalkyler (eller Cost Benefit Analysis, CBA, som de också kallas) är en metod som används inom olika s…</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
         </is>
@@ -3344,15 +4124,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+          <t>2007-09-05</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen behandlar matematiska metoder för statisk optimering. Efter genomgången kurs skall studenten kunna förstår och ha…</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
         </is>
@@ -3371,15 +4157,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten utvecklar sin förmåga att självständigt genomföra forskning kring ett nationalek…</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
@@ -3398,15 +4190,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten tillägnar sig färdigheter att konstruera avancerade ekonometriska modeller med h…</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
@@ -3425,15 +4223,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
@@ -3452,15 +4256,25 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande skall vidareutveckla sin kunskap om och förståelse för lärande …</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
         </is>
@@ -3479,15 +4293,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
         </is>
@@ -3506,15 +4330,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
@@ -3533,15 +4367,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i att dokumentera och upprätta utvecklingsp…</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
         </is>
@@ -3560,15 +4404,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>2007-03-22</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är…</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
@@ -3587,15 +4437,25 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2008-09-16</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
         </is>
@@ -3614,15 +4474,25 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-10-29</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
         </is>
@@ -3641,15 +4511,25 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-12-07</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
         </is>
@@ -3668,15 +4548,25 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-04-05</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
         </is>
@@ -3695,15 +4585,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-02-25</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>2013-11-08</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
         </is>
@@ -3722,15 +4622,25 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-02-25</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
         </is>
@@ -3749,15 +4659,25 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-06</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
         </is>
@@ -3776,15 +4696,25 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-06</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
         </is>
@@ -3803,15 +4733,25 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-06</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
@@ -3830,15 +4770,25 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-06</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
         </is>
@@ -3857,15 +4807,25 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-06</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
         </is>
@@ -3884,15 +4844,25 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-06</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt …</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
@@ -3911,15 +4881,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+          <t>2013-11-06</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
@@ -3938,15 +4914,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-11</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
         </is>
@@ -3965,15 +4951,25 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-11</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
         </is>
@@ -3992,15 +4988,25 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-11</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
         </is>
@@ -4019,15 +5025,25 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
         </is>
@@ -4046,15 +5062,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2014-02-13</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
         </is>
@@ -4073,15 +5095,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+          <t>2014-06-12</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
         </is>
@@ -4100,15 +5128,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+          <t>2014-06-12</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
         </is>
@@ -4127,15 +5161,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
+          <t>2014-06-12</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
         </is>
@@ -4154,15 +5194,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
+          <t>2014-08-21</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
         </is>
@@ -4181,15 +5227,25 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
@@ -4208,15 +5264,25 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
         </is>
@@ -4235,15 +5301,25 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-03-13</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>2013-11-20</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
         </is>
@@ -4262,15 +5338,25 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2007-03-22</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>2011-11-11</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
@@ -4289,15 +5375,25 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-10-07</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>2011-11-11</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
         </is>
@@ -4316,15 +5412,25 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att ge forskarstuderande en introduktion till olika forskningsmetoder samt stödja …</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
@@ -4343,15 +5449,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att de forskarstuderande utvecklar fördjupad kunskap om forskning om läsinlärning o…</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
@@ -4370,15 +5482,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de forskarstuderande utvecklarfördjupade kunskaper om vetenskapsteori och forskningsetik…</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
@@ -4397,15 +5515,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+          <t>2020-12-02</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
@@ -4424,15 +5548,21 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen avser att ge en introduktion till och en översikt av grundläggande statistiska begrepp och deras tillämpning i kv…</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
@@ -4451,15 +5581,21 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
@@ -4478,15 +5614,21 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
@@ -4505,15 +5647,21 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
@@ -4532,15 +5680,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
@@ -4559,15 +5713,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
@@ -4586,15 +5746,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+          <t>2021-01-28</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
@@ -4613,15 +5779,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
@@ -4640,15 +5812,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
@@ -4667,15 +5845,21 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
@@ -4694,15 +5878,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
         </is>
@@ -4721,15 +5911,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
@@ -4748,15 +5944,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
@@ -4775,15 +5977,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
@@ -4802,15 +6010,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
@@ -4829,15 +6043,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
+          <t>2017-01-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
         </is>
@@ -4856,15 +6076,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
@@ -4883,15 +6109,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
@@ -4910,15 +6142,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
+          <t>2020-02-24</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
@@ -4937,15 +6175,25 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
@@ -4964,15 +6212,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
+          <t>2020-02-25</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
@@ -4991,15 +6245,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+          <t>2020-04-23</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
@@ -5018,15 +6278,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
@@ -5045,15 +6311,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
@@ -5072,15 +6344,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
@@ -5099,15 +6377,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
@@ -5126,15 +6410,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
@@ -5153,15 +6443,21 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
@@ -5180,15 +6476,21 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
+          <t>2018-04-12</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
@@ -5207,15 +6509,25 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2018-03-08</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
@@ -5234,15 +6546,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
@@ -5261,15 +6579,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
+          <t>2021-02-08</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
@@ -5288,15 +6612,21 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
+          <t>2021-02-08</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
@@ -5315,15 +6645,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
@@ -5342,15 +6678,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
@@ -5369,15 +6711,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
+          <t>2021-10-08</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
@@ -5396,15 +6744,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
+          <t>2021-10-08</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
@@ -5423,15 +6777,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
+          <t>2021-11-24</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
@@ -5450,15 +6810,21 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
+          <t>2021-11-24</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
@@ -5477,15 +6843,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
@@ -5504,15 +6876,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
@@ -5531,15 +6909,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
+          <t>2022-03-15</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
@@ -5558,15 +6942,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
@@ -5585,15 +6975,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
@@ -5612,15 +7008,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
@@ -5639,15 +7041,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
@@ -5666,15 +7074,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
@@ -5693,15 +7107,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
@@ -5720,15 +7140,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
@@ -5747,15 +7173,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
@@ -5774,15 +7206,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
@@ -5801,15 +7239,21 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
@@ -5828,15 +7272,21 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
@@ -5855,15 +7305,21 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
         </is>
@@ -5882,15 +7338,25 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-10-09</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
+          <t>2013-05-15</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
@@ -5909,15 +7375,25 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-03-15</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
+          <t>2014-02-03</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
@@ -5936,15 +7412,25 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-03-15</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
+          <t>2014-02-03</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
@@ -5963,15 +7449,21 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
@@ -5990,15 +7482,21 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
@@ -6017,15 +7515,25 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
+          <t>2017-11-22</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
@@ -6044,15 +7552,21 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
@@ -6071,15 +7585,25 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
+          <t>2017-01-25</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
@@ -6098,15 +7622,25 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
+          <t>2019-03-15</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
@@ -6125,15 +7659,25 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
+          <t>2018-04-12</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
@@ -6152,15 +7696,21 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
@@ -6179,15 +7729,21 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
@@ -6206,15 +7762,21 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
@@ -6233,15 +7795,21 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
+          <t>2023-01-12</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
@@ -6260,15 +7828,25 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
+          <t>2018-12-21</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
@@ -6287,15 +7865,21 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
@@ -6314,15 +7898,21 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
@@ -6341,15 +7931,21 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
@@ -6368,15 +7964,21 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
@@ -6395,15 +7997,21 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
+          <t>2008-06-10</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
@@ -6422,15 +8030,21 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
+          <t>2013-05-23</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
@@ -6449,15 +8063,21 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
@@ -6476,15 +8096,21 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
@@ -6503,15 +8129,21 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
@@ -6530,15 +8162,21 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
+          <t>2015-02-26</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
@@ -6557,15 +8195,21 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
+          <t>2015-02-26</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
@@ -6584,15 +8228,21 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
+          <t>2015-02-26</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
@@ -6611,15 +8261,21 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
+          <t>2015-02-26</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
@@ -6638,15 +8294,21 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
@@ -6665,15 +8327,21 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
@@ -6692,15 +8360,21 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
@@ -6719,15 +8393,21 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
@@ -6746,15 +8426,21 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
@@ -6773,15 +8459,21 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
@@ -6800,15 +8492,21 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
@@ -6827,15 +8525,21 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
+          <t>2014-01-30</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
@@ -6854,15 +8558,21 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
+          <t>2016-03-24</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
         </is>
@@ -6881,15 +8591,25 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-03-14</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
         </is>
@@ -6908,15 +8628,21 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
         </is>
@@ -6935,503 +8661,509 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E241"/>
+  <autoFilter ref="A1:G241"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId344"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId376"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId386"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId388"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId390"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId394"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId400"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId412"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId414"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId416"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId418"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId420"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId422"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId426"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId430"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId432"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId434"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId436"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId438"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId440"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId442"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId446"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId450"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId452"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId456"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId458"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId462"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId468"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId470"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId472"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId474"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId478"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId480"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt få e…</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur vetenskap och beprövad erfarenhet kan …</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4394,7 +4394,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE1039</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4404,10 +4404,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2007-03-22</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>2008-09-16</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4415,19 +4419,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PE1039</t>
+          <t>PE1050</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4437,7 +4441,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2008-09-16</t>
+          <t>2010-10-29</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4452,19 +4456,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med denna kurs är att de studerande efter avslutad kurs skall förstå den centrala betydelse som l…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PE1050</t>
+          <t>PE1052</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4474,7 +4478,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2010-10-29</t>
+          <t>2010-12-07</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4489,19 +4493,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla deltagarnas kunskaper och färdigheter för att möta barn och elever i behov av sär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PE1052</t>
+          <t>PE1055</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4511,7 +4515,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2010-12-07</t>
+          <t>2012-04-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4526,19 +4530,19 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att de studerande ska ha kunskaper om och förståelse för de regelsystem som gäller för svensk …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PE1055</t>
+          <t>PE1057</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4548,12 +4552,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2012-04-05</t>
+          <t>2013-02-25</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2013-03-06</t>
+          <t>2013-11-08</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4563,19 +4567,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskaper om specialpedagogik och hur barns språk-, …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PE1057</t>
+          <t>PE1058</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4590,7 +4594,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2013-11-08</t>
+          <t>2013-03-06</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4600,19 +4604,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande målsättning är att den studerande tillägnar sig grundläggande förståelse för likabehandling som gru…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PE1058</t>
+          <t>PE1062</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4622,12 +4626,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2013-02-25</t>
+          <t>2013-11-06</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2013-03-06</t>
+          <t>2014-01-24</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4637,19 +4641,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att utveckla kunskap om hur förskolans och skolans lärandemiljöer kan utvecklas med hjälp av I…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>PE1062</t>
+          <t>PE1063</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4674,19 +4678,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en historisk bakgrund inom utveckling av utbildning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>PE1063</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4711,19 +4715,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kännedom om hur undervisning, lärande och kommunikat…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>PE1065</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4748,19 +4752,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande ska visa kännedom om hur examination kan ske via nätet samt vilka …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PE1065</t>
+          <t>PE1066</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4785,19 +4789,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur sociala medier och mol…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>PE1066</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4822,19 +4826,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig en grundläggande kännedom om det rättsliga läget vad…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt få e…</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4847,11 +4851,7 @@
           <t>2013-11-06</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2014-01-24</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4859,19 +4859,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande förstår hur man kan styra sina informationsflöden för att på så sätt få e…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>PE1069</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4881,10 +4881,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2013-11-06</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>2013-11-11</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4892,19 +4896,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kännedom om hur delningskultur och öpp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>PE1069</t>
+          <t>PE1070</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4929,19 +4933,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande finner former för att utveckla kurser inom Nästa generations läran…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>PE1070</t>
+          <t>PE1071</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4966,19 +4970,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande utvecklar förståelse för hur utbildning med stöd av IT kan organis…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>PE1071</t>
+          <t>PE1072</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5003,19 +5007,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig kunskap om på vilka sätt fusk och plagiat kan ta sig…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>PE1072</t>
+          <t>PE1073</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5025,14 +5029,10 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2013-11-11</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2014-01-24</t>
-        </is>
-      </c>
+          <t>2014-02-13</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -5040,19 +5040,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande lärandemål är att den studerande tillägnar sig grundläggande kunskaper om hur mobil teknik kan inte…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>PE1073</t>
+          <t>PE1074</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2014-02-13</t>
+          <t>2014-06-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -5073,19 +5073,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig grundläggande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PE1074</t>
+          <t>PE1075</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>PE1075</t>
+          <t>PE1076</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5139,19 +5139,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur lärandemiljöer kan utvecklas med hjälp av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>PE1076</t>
+          <t>PE1077</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2014-06-12</t>
+          <t>2014-08-21</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -5172,19 +5172,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande tillägnar sig kunskap om hur omvänt klassrum (flippat klassrum) kan anv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>PE1077</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5194,10 +5194,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2014-08-21</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -5205,19 +5209,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>PE2017</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5227,7 +5231,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5242,19 +5246,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande skall utveckla sina kunskaper i bemötandet av barn och elever i behov av …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>PE2017</t>
+          <t>PE3003</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5264,12 +5268,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2012-09-20</t>
+          <t>2007-03-13</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2013-03-06</t>
+          <t>2013-11-20</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5279,19 +5283,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att den studerande ska kunna kritiskt granska teorier och praktik gällande dokumentation i för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PE3003</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5301,12 +5305,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2007-03-13</t>
+          <t>2007-03-22</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2013-11-20</t>
+          <t>2011-11-11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5316,19 +5320,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studerande utvecklar kunskaper om genusteorier med fokus på mansforskning.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>PE3012</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5338,7 +5342,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2007-03-22</t>
+          <t>2010-10-07</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5353,34 +5357,34 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den behörighetsgivande högskolepedagogiska utbildningens övergripande mål är att kursdeltagaren skall ha utvecklat kunsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PE3012</t>
+          <t>FPA0001</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2010-10-07</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2011-11-11</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5390,19 +5394,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att deltagarna ska tillägna sig kunskaper och färdigheter som behövs för att leda kvalificerad…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att ge forskarstuderande en introduktion till olika forskningsmetoder samt stödja …</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>FPA0001</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5412,14 +5416,10 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2018-01-25</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2021-11-18</t>
-        </is>
-      </c>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -5427,19 +5427,19 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att ge forskarstuderande en introduktion till olika forskningsmetoder samt stödja …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att de forskarstuderande utvecklar fördjupad kunskap om forskning om läsinlärning o…</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>FPA2226</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2019-10-23</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -5460,19 +5460,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att de forskarstuderande utvecklar fördjupad kunskap om forskning om läsinlärning o…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de forskarstuderande utvecklarfördjupade kunskaper om vetenskapsteori och forskningsetik…</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>FPA222A</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -5493,19 +5493,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de forskarstuderande utvecklarfördjupade kunskaper om vetenskapsteori och forskningsetik…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>FPA222B</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -5526,19 +5526,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen avser att ge en introduktion till och en översikt av grundläggande statistiska begrepp och deras tillämpning i kv…</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>FPA222J</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -5559,29 +5559,29 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen avser att ge en introduktion till och en översikt av grundläggande statistiska begrepp och deras tillämpning i kv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>FPA222N</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -5592,19 +5592,19 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att de forskarstuderande utvecklar fördjupad kunskap och förståelse av olika metod…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5625,19 +5625,19 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska skaffa sig fördjupade kunskaper om och förståelse för strukturella och socia…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -5658,19 +5658,19 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande ska erhålla en grundläggande förståelse för hur personalekonomi och för…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -5691,19 +5691,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -5724,19 +5724,19 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten, utifrån ett strukturellt och organisatoriskt perspektiv, ska utveckl…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -5757,19 +5757,19 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att introducera studenten i kunskapsområdet som rör personalfrågor, dess sammanhang och begrepp. Kurs…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -5790,19 +5790,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att behandla generella teorier inom strategiområdet. Speciellt kommer kopplingen me…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -5823,19 +5823,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla studentens ämneskunskap om organisationsförändringar som innefattar personalned…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>GPA32E</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5856,19 +5856,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska förstå hur vuxna människor lär och hur kompetensutveckling kan sk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GPA32E</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -5889,19 +5889,19 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att studenten ska utveckla en förmåga att främja kollektivt lärande i en organisation.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5922,19 +5922,19 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att studenten efter avslutad kurs självständigt ska kunna genomföra ett mindre forskningsproje…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5955,19 +5955,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna göra teoretiska analyser av ett forskningsfält och utifrån dess…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -5988,29 +5988,29 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att studenten ska kunna göra metodologiska överväganden i relation till olika forsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>APG22X</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2017-01-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -6021,19 +6021,19 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Syftet med kursen är att den studerande ska tillägna sig djupare kunskaper och färdigheter som en personalvetare behöver…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APG22X</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2017-01-16</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -6054,19 +6054,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om ett område inom utbildningsvetenskaplig fors…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6087,19 +6087,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om vetenskapsteori och kvalitativa och kvantitativ…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>APG24D</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -6120,19 +6120,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>APG24D</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6145,7 +6145,11 @@
           <t>2020-02-24</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -6153,19 +6157,19 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskaper om bedömning och betygssättning inom grundskolans …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6175,14 +6179,10 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2020-02-24</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
+          <t>2020-02-25</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -6190,19 +6190,19 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupade kunskaper om vetenskapsteori, kvalitativa och kva…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2020-02-25</t>
+          <t>2020-04-23</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -6223,19 +6223,19 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla kunskap om utvärdering och utveckling av pedagogisk verksamh…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur vetenskap och beprövad erfarenhet kan …</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2020-04-23</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -6256,19 +6256,19 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur vetenskap och beprövad erfarenhet kan …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -6289,19 +6289,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar sin förmåga att leda didaktiska analytiska samtal genom att gen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6322,19 +6322,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en förståelse för skolor som organisationer och det ansvar som …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -6355,19 +6355,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>APG29G</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -6388,19 +6388,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -6421,19 +6421,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål är att den studerande utvecklar sin förmåga att leda professionsutvecklande insatser grundat i praktikn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -6454,19 +6454,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6476,10 +6476,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>2018-03-08</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -6487,19 +6491,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla god beredskap för att fullgöra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6509,14 +6513,10 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2018-03-08</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -6524,19 +6524,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning med anknytn…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -6557,19 +6557,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka utbildade lärare i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6595,14 +6595,14 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -6623,19 +6623,19 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -6661,14 +6661,14 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6727,14 +6727,14 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -6760,14 +6760,14 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2021-11-24</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -6821,19 +6821,19 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6854,19 +6854,19 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar en teoretisk-kritisk bas för att skapa beredskap att förstå de …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -6887,19 +6887,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -6920,19 +6920,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -6953,19 +6953,19 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av två delkurser.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -7019,19 +7019,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7057,14 +7057,14 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7085,19 +7085,19 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sin didaktiska förmåga att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7123,14 +7123,14 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7151,19 +7151,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla sitt pedagogiska ledarskap där förmågan att kommunicera och aktiv…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -7184,19 +7184,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7222,14 +7222,14 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -7250,19 +7250,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3JD</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -7283,19 +7283,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Mål saknas.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GPG3JD</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7305,10 +7305,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>2012-10-09</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2013-05-15</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7316,19 +7320,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla grundläggande kunskaper, färdigheter och förhållningssätt i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7338,12 +7342,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2012-10-09</t>
+          <t>2013-03-15</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2013-05-15</t>
+          <t>2014-02-03</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7358,14 +7362,14 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7390,19 +7394,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en självständig vetenskaplig undersökning inom något …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7412,14 +7416,10 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2013-03-15</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>2014-02-03</t>
-        </is>
-      </c>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7427,19 +7427,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
+          <t>2013-07-03</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -7465,14 +7465,14 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7482,10 +7482,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2017-11-22</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7493,19 +7497,19 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om olika pedagogiska och specialpedagogiska persp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7515,14 +7519,10 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2017-11-22</t>
-        </is>
-      </c>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7530,19 +7530,19 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Ett övergripande mål för kursen är att problematisera relationen mellan utbildningsfilosofiska teorier och olika argumen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7552,10 +7552,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2017-01-25</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7563,19 +7567,19 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad kunskap om centrala teoribildningar inom det utbildning…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7585,12 +7589,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2017-01-25</t>
+          <t>2019-03-15</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7600,19 +7604,19 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om hur olika vetenskapliga perspektiv på den …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>PG3069</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7622,12 +7626,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2019-03-15</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7637,36 +7641,32 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att deltagarna utvecklar fördjupad förmåga att kritiskt granska och värdera utbildningsvet…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>PG3069</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7674,19 +7674,19 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7707,19 +7707,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är uppdelade per delkurs.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -7740,19 +7740,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -7773,19 +7773,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7795,10 +7795,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>2016-09-13</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2018-12-21</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7806,36 +7810,32 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för religionskunskapsundervisning inom gymnasieskolan.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2018-12-21</t>
-        </is>
-      </c>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -7843,19 +7843,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Övergripande mål för kursen är att studenten ska utveckla förmåga att planera och genomföra en vetenskaplig förstudie so…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -7876,19 +7876,19 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla grundläggande kunskaper och färdigheter för att kunna hantera jur…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -7909,19 +7909,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -7942,19 +7942,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten ska kunna hantera vanligtvis förekommande frågeställningar inom rätt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2008-06-10</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -7975,19 +7975,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Under kursen ska studenten utveckla grundläggande kunskaper, färdigheter och förmågor för att kunna hantera juridiska fr…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2008-06-10</t>
+          <t>2013-05-23</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -8008,19 +8008,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med utgångspunkt i teorier samt egna och andras erfarenheter av verksamhe…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2013-05-23</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -8041,19 +8041,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska utveckla en förmåga att avgöra lämplig anställningsform utifrån reglerna i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8107,19 +8107,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -8140,19 +8140,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper, färdigheter och förhållningssätt för a…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8173,19 +8173,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera I…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8239,19 +8239,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter inom de civilrättsliga …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2015-02-26</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -8272,19 +8272,19 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla grundläggande kunskaper och färdigheter för att kunna hantera j…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8305,19 +8305,19 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall utveckla sin förståelse för den svenska idrottsrörelsens juridiska förut…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8343,24 +8343,24 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -8371,19 +8371,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål och syfte är att studenten skall utveckla grundläggande kunskap, färdigheter och förhållningssä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -8404,19 +8404,19 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska skaffa sig grundläggande kunskaper om och förståelse för soc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8437,19 +8437,19 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -8475,24 +8475,24 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2014-01-30</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -8503,19 +8503,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade kunskaper om teorier och metoder som använd…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>TR2005</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2014-01-30</t>
+          <t>2016-03-24</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -8536,19 +8536,19 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen är uppbyggd av tre moduler som examineras i tur och ordning.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>TR2005</t>
+          <t>TR3008</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8558,10 +8558,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2016-03-24</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2013-03-14</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -8569,36 +8573,32 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinatio…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>TR3008</t>
+          <t>AS4001</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2013-09-18</t>
-        </is>
-      </c>
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -8606,19 +8606,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper i turismvetenskap med särskild bäring på destinations…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>AS4001</t>
+          <t>AS4002</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8639,50 +8639,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bli väl förtrogen med ett avgränsat och specifikt kunskapsområde inom…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>AS4002</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>2016-05-03</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda den studerande för att skriva ett examensarbete på masternivå i Afrikanska stu…</t>
-        </is>
-      </c>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G241"/>
+  <autoFilter ref="A1:G240"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -9162,8 +9129,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId480"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
